--- a/2026/GENERAL PAZ 138/Mayo/Mayo GRAL PAZ 138.xlsx
+++ b/2026/GENERAL PAZ 138/Mayo/Mayo GRAL PAZ 138.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GENERAL PAZ 138\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF70DEAB-8400-4078-BD81-0C7172B83817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3DFD8E-F6D2-4D4E-9641-D24BBAAC7B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$91</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$90</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -300,19 +305,16 @@
     <t>MARSANO ADRIANA</t>
   </si>
   <si>
-    <t>Recupero de fondo inicial puesto por administracion entrante</t>
-  </si>
-  <si>
     <t>FED. PATRONAL - Seguro integral - Póliza Nº 2318491</t>
   </si>
   <si>
     <t>VTO 18/06</t>
   </si>
   <si>
-    <t>Honorarios administracion - SE ADEUDA MAYO</t>
-  </si>
-  <si>
     <t>Transf 22/05</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Abril y Mayo</t>
   </si>
 </sst>
 </file>
@@ -328,7 +330,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -613,13 +615,6 @@
       <b/>
       <sz val="10"/>
       <name val="Arial1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1331,7 +1326,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1558,6 +1553,54 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1567,56 +1610,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="42" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -1726,9 +1720,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1766,9 +1760,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1801,9 +1795,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1836,9 +1847,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2012,17 +2040,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L91"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L90"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2041,7 +2069,7 @@
       <c r="C2" s="78"/>
       <c r="D2" s="78"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="78"/>
       <c r="B3" s="78"/>
       <c r="C3" s="78"/>
@@ -2075,7 +2103,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2112,10 +2140,10 @@
       <c r="D17" s="154"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1"/>
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1"/>
     <row r="21" spans="1:7">
       <c r="A21" s="6" t="s">
         <v>18</v>
@@ -2215,13 +2243,14 @@
       </c>
       <c r="B32" s="123"/>
       <c r="C32" s="91">
-        <v>0</v>
+        <f>65000*2</f>
+        <v>130000</v>
       </c>
       <c r="D32" s="89"/>
       <c r="F32" s="22"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1">
       <c r="A33" s="14" t="s">
         <v>26</v>
       </c>
@@ -2229,7 +2258,7 @@
       <c r="C33" s="19"/>
       <c r="D33" s="56">
         <f>SUM(C32:C32)</f>
-        <v>0</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" customHeight="1">
@@ -2240,17 +2269,17 @@
       <c r="C34" s="17"/>
       <c r="D34" s="33"/>
     </row>
-    <row r="35" spans="1:6" ht="41.4" customHeight="1">
+    <row r="35" spans="1:6" ht="18.75" customHeight="1">
       <c r="A35" s="152" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B35" s="153"/>
-      <c r="C35" s="180">
+      <c r="C35" s="179">
         <v>87914</v>
       </c>
       <c r="D35" s="88"/>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1">
+    <row r="36" spans="1:6" ht="15.75" thickBot="1">
       <c r="A36" s="14" t="s">
         <v>1</v>
       </c>
@@ -2334,11 +2363,11 @@
         <v>83</v>
       </c>
       <c r="B44" s="54"/>
-      <c r="C44" s="179">
+      <c r="C44" s="94">
         <v>36475.68</v>
       </c>
       <c r="D44" s="86" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1">
@@ -2346,14 +2375,14 @@
         <v>80</v>
       </c>
       <c r="B45" s="54"/>
-      <c r="C45" s="179">
+      <c r="C45" s="94">
         <v>197470.88</v>
       </c>
       <c r="D45" s="86" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1">
       <c r="A46" s="14" t="s">
         <v>3</v>
       </c>
@@ -2364,7 +2393,7 @@
         <v>233946.56</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1">
+    <row r="47" spans="1:6" ht="15.75" thickBot="1">
       <c r="A47" s="13" t="s">
         <v>28</v>
       </c>
@@ -2372,13 +2401,13 @@
       <c r="C47" s="19"/>
       <c r="D47" s="61"/>
     </row>
-    <row r="48" spans="1:6" ht="19.95" customHeight="1">
+    <row r="48" spans="1:6" ht="19.899999999999999" customHeight="1">
       <c r="A48" s="152"/>
       <c r="B48" s="153"/>
       <c r="C48" s="94"/>
       <c r="D48" s="84"/>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1">
+    <row r="49" spans="1:6" ht="15.75" thickBot="1">
       <c r="A49" s="14" t="s">
         <v>11</v>
       </c>
@@ -2389,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1">
+    <row r="50" spans="1:6" ht="15.75" thickBot="1">
       <c r="A50" s="13" t="s">
         <v>21</v>
       </c>
@@ -2403,7 +2432,7 @@
       <c r="C51" s="96"/>
       <c r="D51" s="64"/>
     </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1">
+    <row r="52" spans="1:6" ht="15.75" thickBot="1">
       <c r="A52" s="126" t="s">
         <v>26</v>
       </c>
@@ -2414,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1">
+    <row r="53" spans="1:6" ht="15.75" thickBot="1">
       <c r="A53" s="54"/>
       <c r="B53" s="54"/>
       <c r="C53" s="54"/>
@@ -2426,16 +2455,19 @@
       </c>
       <c r="B54" s="157"/>
       <c r="C54" s="158"/>
-      <c r="D54" s="67"/>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1">
+      <c r="D54" s="67">
+        <f>1000000-451860.56</f>
+        <v>548139.43999999994</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1">
       <c r="A55" s="127"/>
       <c r="B55" s="68"/>
       <c r="C55" s="68"/>
       <c r="D55" s="69"/>
       <c r="E55" s="23"/>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1">
+    <row r="56" spans="1:6" ht="15.75" thickBot="1">
       <c r="A56" s="128" t="s">
         <v>22</v>
       </c>
@@ -2443,7 +2475,7 @@
       <c r="C56" s="70"/>
       <c r="D56" s="71">
         <f>(SUM(D25:D54))</f>
-        <v>321860.56</v>
+        <v>1000000</v>
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="23"/>
@@ -2455,7 +2487,7 @@
       <c r="D57" s="68"/>
       <c r="F57" s="83"/>
     </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1">
+    <row r="58" spans="1:6" ht="15.75" thickBot="1">
       <c r="A58" s="68"/>
       <c r="B58" s="68"/>
       <c r="C58" s="68"/>
@@ -2516,12 +2548,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15" thickBot="1">
+    <row r="67" spans="1:4" ht="15.75" thickBot="1">
       <c r="A67" s="68"/>
       <c r="B67" s="68"/>
       <c r="C67" s="68"/>
     </row>
-    <row r="68" spans="1:4" ht="15" thickBot="1">
+    <row r="68" spans="1:4" ht="15.75" thickBot="1">
       <c r="A68" s="128" t="s">
         <v>33</v>
       </c>
@@ -2532,32 +2564,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" thickBot="1">
+    <row r="69" spans="1:4" ht="15.75" thickBot="1">
       <c r="A69" s="68"/>
       <c r="B69" s="68"/>
       <c r="C69" s="68"/>
     </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1">
+    <row r="70" spans="1:4" ht="15.75" thickBot="1">
       <c r="A70" s="141" t="s">
         <v>23</v>
       </c>
       <c r="B70" s="142">
         <f>D56</f>
-        <v>321860.56</v>
+        <v>1000000</v>
       </c>
       <c r="C70" s="143"/>
     </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1">
+    <row r="71" spans="1:4" ht="15.75" thickBot="1">
       <c r="A71" s="141" t="s">
         <v>24</v>
       </c>
       <c r="B71" s="142">
         <f>D56-D54</f>
-        <v>321860.56</v>
+        <v>451860.56000000006</v>
       </c>
       <c r="C71" s="68"/>
     </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1">
+    <row r="72" spans="1:4" ht="15.75" thickBot="1">
       <c r="A72" s="141" t="s">
         <v>34</v>
       </c>
@@ -2567,7 +2599,7 @@
       </c>
       <c r="C72" s="68"/>
     </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1">
+    <row r="73" spans="1:4" ht="15.75" thickBot="1">
       <c r="A73" s="141" t="s">
         <v>49</v>
       </c>
@@ -2592,7 +2624,7 @@
       <c r="B76" s="68"/>
       <c r="C76" s="68"/>
     </row>
-    <row r="77" spans="1:4" ht="15" thickBot="1">
+    <row r="77" spans="1:4" ht="15.75" thickBot="1">
       <c r="A77" s="144" t="s">
         <v>44</v>
       </c>
@@ -2604,7 +2636,7 @@
         <v>25</v>
       </c>
       <c r="B78" s="146">
-        <v>6092.56</v>
+        <v>7678.890000000014</v>
       </c>
       <c r="C78" s="68"/>
     </row>
@@ -2614,100 +2646,91 @@
       </c>
       <c r="B79" s="62">
         <f>PRORRATEO!H18</f>
-        <v>837834</v>
+        <v>531811.4</v>
       </c>
       <c r="C79" s="68"/>
     </row>
     <row r="80" spans="1:4" ht="14.25" customHeight="1">
       <c r="A80" s="147" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B80" s="62">
-        <v>-521370</v>
+        <f>B89</f>
+        <v>0</v>
       </c>
       <c r="C80" s="68"/>
     </row>
-    <row r="81" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A81" s="147" t="s">
-        <v>51</v>
+    <row r="81" spans="1:12">
+      <c r="A81" s="149" t="s">
+        <v>35</v>
       </c>
       <c r="B81" s="62">
-        <f>B90</f>
-        <v>0</v>
+        <f>-B71</f>
+        <v>-451860.56000000006</v>
       </c>
       <c r="C81" s="68"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="149" t="s">
-        <v>35</v>
+      <c r="A82" s="148" t="s">
+        <v>36</v>
       </c>
       <c r="B82" s="62">
-        <f>-B71</f>
-        <v>-321860.56</v>
+        <f>-(B72)</f>
+        <v>0</v>
       </c>
       <c r="C82" s="68"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="148" t="s">
-        <v>36</v>
-      </c>
-      <c r="B83" s="62">
-        <f>-(B72)</f>
-        <v>0</v>
-      </c>
-      <c r="C83" s="68"/>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" s="11" t="s">
+      <c r="A83" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B84" s="106">
-        <f>SUM(B78:B83)</f>
-        <v>696.00000000005821</v>
-      </c>
-      <c r="C84" s="133"/>
-    </row>
-    <row r="85" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B85" s="22"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="133"/>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" s="155" t="s">
+      <c r="B83" s="106">
+        <f>SUM(B78:B82)</f>
+        <v>87629.729999999981</v>
+      </c>
+      <c r="C83" s="133"/>
+    </row>
+    <row r="84" spans="1:12" ht="34.5" customHeight="1">
+      <c r="B84" s="22"/>
+      <c r="C84" s="23"/>
+      <c r="D84" s="133"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="155" t="s">
         <v>43</v>
       </c>
+      <c r="B85" s="155"/>
+    </row>
+    <row r="86" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A86" s="155"/>
       <c r="B86" s="155"/>
     </row>
-    <row r="87" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A87" s="155"/>
-      <c r="B87" s="155"/>
+    <row r="87" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A87" s="74"/>
+      <c r="B87" s="18"/>
     </row>
     <row r="88" spans="1:12" ht="32.25" customHeight="1">
       <c r="A88" s="74"/>
       <c r="B88" s="18"/>
     </row>
-    <row r="89" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A89" s="74"/>
-      <c r="B89" s="18"/>
+    <row r="89" spans="1:12">
+      <c r="A89" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="75">
+        <f>SUM(B87:B88)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:12">
-      <c r="A90" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B90" s="75">
-        <f>SUM(B88:B89)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12">
-      <c r="L91" s="4"/>
+      <c r="L90" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A86:B87"/>
+    <mergeCell ref="A85:B86"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="B9:B11"/>
@@ -2723,45 +2746,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.9" customHeight="1">
+    <row r="1" spans="1:21" ht="12.95" customHeight="1">
       <c r="A1" s="107"/>
-      <c r="B1" s="164" t="str">
+      <c r="B1" s="160" t="str">
         <f>RESUMEN!A4</f>
         <v>TRANSFERIR A  : carolina.rc.adm - CVU: 0000003100054616492658</v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
       <c r="L1" s="108"/>
       <c r="M1" s="108"/>
       <c r="N1" s="108"/>
@@ -2770,23 +2793,23 @@
     </row>
     <row r="2" spans="1:21" ht="14.25" customHeight="1">
       <c r="A2" s="110"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
       <c r="L2" s="111"/>
       <c r="M2" s="111" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="118">
-        <v>314877</v>
+        <v>1000000</v>
       </c>
       <c r="P2" s="112"/>
       <c r="Q2" s="9"/>
@@ -2796,16 +2819,16 @@
     </row>
     <row r="3" spans="1:21" ht="16.5" customHeight="1" thickBot="1">
       <c r="A3" s="113"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="166"/>
-      <c r="E3" s="166"/>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
+      <c r="B3" s="162"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="162"/>
       <c r="L3" s="114"/>
       <c r="M3" s="114" t="s">
         <v>53</v>
@@ -2818,96 +2841,96 @@
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="176" t="s">
+      <c r="B4" s="173" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="177"/>
-      <c r="D4" s="177"/>
-      <c r="E4" s="177"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="177"/>
-      <c r="H4" s="177"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="177"/>
-      <c r="K4" s="177"/>
-      <c r="L4" s="177"/>
-      <c r="M4" s="177"/>
-      <c r="N4" s="177"/>
-      <c r="O4" s="177"/>
-      <c r="P4" s="178"/>
+      <c r="C4" s="174"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="174"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="174"/>
+      <c r="J4" s="174"/>
+      <c r="K4" s="174"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="175"/>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="160" t="s">
+      <c r="A5" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="162" t="s">
+      <c r="B5" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="163" t="s">
+      <c r="C5" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="163" t="s">
+      <c r="D5" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="163" t="s">
+      <c r="E5" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="163" t="s">
+      <c r="F5" s="165" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="163" t="s">
+      <c r="G5" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="163" t="s">
+      <c r="H5" s="165" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="163" t="s">
+      <c r="I5" s="165" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="172" t="s">
+      <c r="J5" s="169" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="170" t="s">
+      <c r="K5" s="167" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="170" t="s">
+      <c r="L5" s="167" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="170" t="s">
+      <c r="M5" s="167" t="s">
         <v>37</v>
       </c>
-      <c r="N5" s="174" t="s">
+      <c r="N5" s="171" t="s">
         <v>48</v>
       </c>
       <c r="O5" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="167" t="s">
+      <c r="P5" s="163" t="s">
         <v>46</v>
       </c>
       <c r="S5" s="23"/>
       <c r="T5" s="22"/>
     </row>
     <row r="6" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A6" s="161"/>
-      <c r="B6" s="162"/>
-      <c r="C6" s="163"/>
-      <c r="D6" s="163"/>
-      <c r="E6" s="169"/>
-      <c r="F6" s="163"/>
-      <c r="G6" s="163"/>
-      <c r="H6" s="163"/>
-      <c r="I6" s="169"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="171"/>
-      <c r="L6" s="170"/>
-      <c r="M6" s="171"/>
-      <c r="N6" s="175"/>
+      <c r="A6" s="177"/>
+      <c r="B6" s="178"/>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="166"/>
+      <c r="J6" s="170"/>
+      <c r="K6" s="168"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="168"/>
+      <c r="N6" s="172"/>
       <c r="O6" s="29" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="P6" s="167"/>
+      <c r="P6" s="163"/>
       <c r="S6" s="22">
         <v>65160</v>
       </c>
@@ -2937,7 +2960,7 @@
         <v>11.2</v>
       </c>
       <c r="G7" s="36">
-        <v>1118684</v>
+        <v>1187511.01</v>
       </c>
       <c r="H7" s="37">
         <v>0</v>
@@ -2945,11 +2968,11 @@
       <c r="I7" s="38"/>
       <c r="J7" s="39">
         <f>G7-H7</f>
-        <v>1118684</v>
+        <v>1187511.01</v>
       </c>
       <c r="K7" s="39">
         <f>IF(J7&gt;0,J7*3%,0)</f>
-        <v>33560.519999999997</v>
+        <v>35625.330300000001</v>
       </c>
       <c r="L7" s="150">
         <f>O$3*F7%</f>
@@ -2957,18 +2980,18 @@
       </c>
       <c r="M7" s="40">
         <f>O$2*F7%</f>
-        <v>35266.223999999995</v>
+        <v>111999.99999999999</v>
       </c>
       <c r="N7" s="41">
         <v>0</v>
       </c>
       <c r="O7" s="42">
         <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>1187511.01</v>
+        <v>1335136.01</v>
       </c>
       <c r="P7" s="43">
         <f t="shared" ref="P7:P16" si="0">ROUND(O7*3%,0) + O7</f>
-        <v>1223136.01</v>
+        <v>1375190.01</v>
       </c>
       <c r="Q7" s="23">
         <v>0.01</v>
@@ -3002,19 +3025,19 @@
         <v>11.2</v>
       </c>
       <c r="G8" s="36">
-        <v>867688</v>
+        <v>815685.02</v>
       </c>
       <c r="H8" s="37">
-        <v>110000</v>
+        <v>300000</v>
       </c>
       <c r="I8" s="38"/>
       <c r="J8" s="39">
         <f t="shared" ref="J8:J16" si="2">G8-H8</f>
-        <v>757688</v>
+        <v>515685.02</v>
       </c>
       <c r="K8" s="39">
         <f t="shared" ref="K8:K16" si="3">IF(J8&gt;0,J8*3%,0)</f>
-        <v>22730.639999999999</v>
+        <v>15470.5506</v>
       </c>
       <c r="L8" s="40">
         <f t="shared" ref="L8:L17" si="4">O$3*F8%</f>
@@ -3022,18 +3045,18 @@
       </c>
       <c r="M8" s="40">
         <f t="shared" ref="M8:M17" si="5">O$2*F8%</f>
-        <v>35266.223999999995</v>
+        <v>111999.99999999999</v>
       </c>
       <c r="N8" s="41">
         <v>0</v>
       </c>
       <c r="O8" s="42">
         <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>815685.02</v>
+        <v>643156.02</v>
       </c>
       <c r="P8" s="43">
         <f t="shared" si="0"/>
-        <v>840156.02</v>
+        <v>662451.02</v>
       </c>
       <c r="Q8" s="23">
         <f>Q7+0.01</f>
@@ -3069,15 +3092,16 @@
         <v>8.9</v>
       </c>
       <c r="G9" s="37">
-        <v>84373</v>
+        <v>23806.03</v>
       </c>
       <c r="H9" s="37">
-        <v>88591</v>
+        <f>G9</f>
+        <v>23806.03</v>
       </c>
       <c r="I9" s="38"/>
       <c r="J9" s="100">
         <f t="shared" si="2"/>
-        <v>-4218</v>
+        <v>0</v>
       </c>
       <c r="K9" s="39">
         <f t="shared" si="3"/>
@@ -3089,18 +3113,18 @@
       </c>
       <c r="M9" s="101">
         <f t="shared" si="5"/>
-        <v>28024.053000000004</v>
+        <v>89000.000000000015</v>
       </c>
       <c r="N9" s="102">
         <v>0</v>
       </c>
       <c r="O9" s="103">
         <f t="shared" ref="O9:O16" si="6">ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>23806.03</v>
+        <v>89000.03</v>
       </c>
       <c r="P9" s="104">
         <f t="shared" si="0"/>
-        <v>24520.03</v>
+        <v>91670.03</v>
       </c>
       <c r="Q9" s="23">
         <f t="shared" ref="Q9:Q16" si="7">Q8+0.01</f>
@@ -3135,16 +3159,15 @@
         <v>8.9</v>
       </c>
       <c r="G10" s="36">
-        <v>84373</v>
+        <v>28024.04</v>
       </c>
       <c r="H10" s="37">
-        <f>G10</f>
-        <v>84373</v>
+        <v>28050</v>
       </c>
       <c r="I10" s="38"/>
       <c r="J10" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-25.959999999999127</v>
       </c>
       <c r="K10" s="39">
         <f t="shared" si="3"/>
@@ -3156,18 +3179,18 @@
       </c>
       <c r="M10" s="40">
         <f t="shared" si="5"/>
-        <v>28024.053000000004</v>
+        <v>89000.000000000015</v>
       </c>
       <c r="N10" s="41">
         <v>0</v>
       </c>
       <c r="O10" s="42">
         <f t="shared" si="6"/>
-        <v>28024.04</v>
+        <v>88974.04</v>
       </c>
       <c r="P10" s="43">
         <f t="shared" si="0"/>
-        <v>28865.040000000001</v>
+        <v>91643.04</v>
       </c>
       <c r="Q10" s="23">
         <f t="shared" si="7"/>
@@ -3202,15 +3225,16 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="G11" s="36">
-        <v>92473</v>
+        <v>26235.05</v>
       </c>
       <c r="H11" s="37">
-        <v>97096</v>
+        <f>G11</f>
+        <v>26235.05</v>
       </c>
       <c r="I11" s="38"/>
       <c r="J11" s="39">
         <f t="shared" si="2"/>
-        <v>-4623</v>
+        <v>0</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="3"/>
@@ -3222,18 +3246,18 @@
       </c>
       <c r="M11" s="40">
         <f t="shared" si="5"/>
-        <v>30857.946</v>
+        <v>98000</v>
       </c>
       <c r="N11" s="41">
         <v>0</v>
       </c>
       <c r="O11" s="42">
         <f t="shared" si="6"/>
-        <v>26235.05</v>
+        <v>98000.05</v>
       </c>
       <c r="P11" s="43">
         <f t="shared" si="0"/>
-        <v>27022.05</v>
+        <v>100940.05</v>
       </c>
       <c r="Q11" s="23">
         <f t="shared" si="7"/>
@@ -3268,11 +3292,11 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="G12" s="36">
-        <v>92473</v>
+        <v>30858.06</v>
       </c>
       <c r="H12" s="37">
         <f>G12</f>
-        <v>92473</v>
+        <v>30858.06</v>
       </c>
       <c r="I12" s="38"/>
       <c r="J12" s="39">
@@ -3289,18 +3313,18 @@
       </c>
       <c r="M12" s="40">
         <f t="shared" si="5"/>
-        <v>30857.946</v>
+        <v>98000</v>
       </c>
       <c r="N12" s="132">
         <v>0</v>
       </c>
       <c r="O12" s="42">
         <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>30858.06</v>
+        <v>98000.06</v>
       </c>
       <c r="P12" s="43">
         <f t="shared" si="0"/>
-        <v>31784.06</v>
+        <v>100940.06</v>
       </c>
       <c r="Q12" s="23">
         <f t="shared" si="7"/>
@@ -3335,10 +3359,11 @@
         <v>8.9</v>
       </c>
       <c r="G13" s="36">
-        <v>84373</v>
+        <v>28024.07</v>
       </c>
       <c r="H13" s="37">
-        <v>84373</v>
+        <f>G13</f>
+        <v>28024.07</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="39">
@@ -3355,18 +3380,18 @@
       </c>
       <c r="M13" s="40">
         <f t="shared" si="5"/>
-        <v>28024.053000000004</v>
+        <v>89000.000000000015</v>
       </c>
       <c r="N13" s="41">
         <v>0</v>
       </c>
       <c r="O13" s="42">
         <f t="shared" si="6"/>
-        <v>28024.07</v>
+        <v>89000.07</v>
       </c>
       <c r="P13" s="43">
         <f t="shared" si="0"/>
-        <v>28865.07</v>
+        <v>91670.07</v>
       </c>
       <c r="Q13" s="23">
         <f t="shared" si="7"/>
@@ -3404,16 +3429,15 @@
         <v>8.9</v>
       </c>
       <c r="G14" s="36">
-        <v>84373</v>
+        <v>28024.080000000002</v>
       </c>
       <c r="H14" s="37">
-        <f>G14</f>
-        <v>84373</v>
+        <v>28865</v>
       </c>
       <c r="I14" s="38"/>
       <c r="J14" s="39">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-840.91999999999825</v>
       </c>
       <c r="K14" s="39">
         <f t="shared" si="3"/>
@@ -3425,18 +3449,18 @@
       </c>
       <c r="M14" s="40">
         <f t="shared" si="5"/>
-        <v>28024.053000000004</v>
+        <v>89000.000000000015</v>
       </c>
       <c r="N14" s="41">
         <v>0</v>
       </c>
       <c r="O14" s="42">
         <f t="shared" si="6"/>
-        <v>28024.080000000002</v>
+        <v>88159.08</v>
       </c>
       <c r="P14" s="43">
         <f t="shared" si="0"/>
-        <v>28865.08</v>
+        <v>90804.08</v>
       </c>
       <c r="Q14" s="23">
         <f t="shared" si="7"/>
@@ -3473,15 +3497,15 @@
         <v>11.2</v>
       </c>
       <c r="G15" s="37">
-        <v>91196</v>
+        <v>30707.09</v>
       </c>
       <c r="H15" s="37">
-        <v>95755</v>
+        <v>30707.09</v>
       </c>
       <c r="I15" s="38"/>
       <c r="J15" s="100">
         <f t="shared" si="2"/>
-        <v>-4559</v>
+        <v>0</v>
       </c>
       <c r="K15" s="100">
         <v>0</v>
@@ -3492,18 +3516,18 @@
       </c>
       <c r="M15" s="101">
         <f t="shared" si="5"/>
-        <v>35266.223999999995</v>
+        <v>111999.99999999999</v>
       </c>
       <c r="N15" s="102">
         <v>0</v>
       </c>
       <c r="O15" s="103">
         <f t="shared" si="6"/>
-        <v>30707.09</v>
+        <v>112000.09</v>
       </c>
       <c r="P15" s="104">
         <f t="shared" si="0"/>
-        <v>31628.09</v>
+        <v>115360.09</v>
       </c>
       <c r="Q15" s="23">
         <f t="shared" si="7"/>
@@ -3520,7 +3544,7 @@
         <v>141245</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="16.2" customHeight="1">
+    <row r="16" spans="1:21" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -3538,10 +3562,11 @@
         <v>11.2</v>
       </c>
       <c r="G16" s="36">
-        <v>100800</v>
+        <v>35266.1</v>
       </c>
       <c r="H16" s="37">
-        <v>100800</v>
+        <f>G16</f>
+        <v>35266.1</v>
       </c>
       <c r="I16" s="38"/>
       <c r="J16" s="39">
@@ -3558,18 +3583,18 @@
       </c>
       <c r="M16" s="40">
         <f t="shared" si="5"/>
-        <v>35266.223999999995</v>
+        <v>111999.99999999999</v>
       </c>
       <c r="N16" s="41">
         <v>0</v>
       </c>
       <c r="O16" s="42">
         <f t="shared" si="6"/>
-        <v>35266.1</v>
+        <v>112000.1</v>
       </c>
       <c r="P16" s="43">
         <f t="shared" si="0"/>
-        <v>36324.1</v>
+        <v>115360.1</v>
       </c>
       <c r="Q16" s="23">
         <f t="shared" si="7"/>
@@ -3586,7 +3611,7 @@
         <v>243540</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" thickBot="1">
+    <row r="17" spans="1:17" ht="15.75" thickBot="1">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -3620,7 +3645,7 @@
       <c r="P17" s="43"/>
       <c r="Q17" s="23"/>
     </row>
-    <row r="18" spans="1:17" ht="15" thickBot="1">
+    <row r="18" spans="1:17" ht="15.75" thickBot="1">
       <c r="B18" s="49"/>
       <c r="C18" s="50"/>
       <c r="D18" s="51"/>
@@ -3631,11 +3656,11 @@
       </c>
       <c r="G18" s="26">
         <f>SUM(G7:G17)</f>
-        <v>2700806</v>
+        <v>2234140.5499999998</v>
       </c>
       <c r="H18" s="30">
         <f>SUM(H7:H17)</f>
-        <v>837834</v>
+        <v>531811.4</v>
       </c>
       <c r="I18" s="30">
         <f>SUM(I7:I17)</f>
@@ -3649,7 +3674,7 @@
       </c>
       <c r="M18" s="30">
         <f>SUM(M7:M17)</f>
-        <v>314877</v>
+        <v>1000000</v>
       </c>
       <c r="N18" s="30">
         <f>SUM(N7:N17)</f>
@@ -3657,11 +3682,11 @@
       </c>
       <c r="O18" s="53">
         <f>SUM(O7:O16)</f>
-        <v>2234140.5499999998</v>
+        <v>2753425.55</v>
       </c>
       <c r="P18" s="53">
         <f>SUM(P7:P16)</f>
-        <v>2301165.5499999998</v>
+        <v>2836028.55</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -3669,93 +3694,98 @@
       <c r="E19" s="25"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="D21" s="168" t="s">
+      <c r="D21" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="168"/>
-      <c r="F21" s="168"/>
-      <c r="G21" s="168"/>
-      <c r="H21" s="168"/>
-      <c r="I21" s="168"/>
-      <c r="J21" s="168"/>
-      <c r="K21" s="168"/>
-      <c r="L21" s="168"/>
-      <c r="M21" s="168"/>
-      <c r="N21" s="168"/>
-      <c r="O21" s="168"/>
+      <c r="E21" s="164"/>
+      <c r="F21" s="164"/>
+      <c r="G21" s="164"/>
+      <c r="H21" s="164"/>
+      <c r="I21" s="164"/>
+      <c r="J21" s="164"/>
+      <c r="K21" s="164"/>
+      <c r="L21" s="164"/>
+      <c r="M21" s="164"/>
+      <c r="N21" s="164"/>
+      <c r="O21" s="164"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="D22" s="168"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="168"/>
-      <c r="G22" s="168"/>
-      <c r="H22" s="168"/>
-      <c r="I22" s="168"/>
-      <c r="J22" s="168"/>
-      <c r="K22" s="168"/>
-      <c r="L22" s="168"/>
-      <c r="M22" s="168"/>
-      <c r="N22" s="168"/>
-      <c r="O22" s="168"/>
+      <c r="D22" s="164"/>
+      <c r="E22" s="164"/>
+      <c r="F22" s="164"/>
+      <c r="G22" s="164"/>
+      <c r="H22" s="164"/>
+      <c r="I22" s="164"/>
+      <c r="J22" s="164"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="164"/>
+      <c r="M22" s="164"/>
+      <c r="N22" s="164"/>
+      <c r="O22" s="164"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="D23" s="168"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="168"/>
-      <c r="G23" s="168"/>
-      <c r="H23" s="168"/>
-      <c r="I23" s="168"/>
-      <c r="J23" s="168"/>
-      <c r="K23" s="168"/>
-      <c r="L23" s="168"/>
-      <c r="M23" s="168"/>
-      <c r="N23" s="168"/>
-      <c r="O23" s="168"/>
+      <c r="D23" s="164"/>
+      <c r="E23" s="164"/>
+      <c r="F23" s="164"/>
+      <c r="G23" s="164"/>
+      <c r="H23" s="164"/>
+      <c r="I23" s="164"/>
+      <c r="J23" s="164"/>
+      <c r="K23" s="164"/>
+      <c r="L23" s="164"/>
+      <c r="M23" s="164"/>
+      <c r="N23" s="164"/>
+      <c r="O23" s="164"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="D24" s="168"/>
-      <c r="E24" s="168"/>
-      <c r="F24" s="168"/>
-      <c r="G24" s="168"/>
-      <c r="H24" s="168"/>
-      <c r="I24" s="168"/>
-      <c r="J24" s="168"/>
-      <c r="K24" s="168"/>
-      <c r="L24" s="168"/>
-      <c r="M24" s="168"/>
-      <c r="N24" s="168"/>
-      <c r="O24" s="168"/>
+      <c r="D24" s="164"/>
+      <c r="E24" s="164"/>
+      <c r="F24" s="164"/>
+      <c r="G24" s="164"/>
+      <c r="H24" s="164"/>
+      <c r="I24" s="164"/>
+      <c r="J24" s="164"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="164"/>
+      <c r="M24" s="164"/>
+      <c r="N24" s="164"/>
+      <c r="O24" s="164"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="D25" s="168"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="168"/>
-      <c r="H25" s="168"/>
-      <c r="I25" s="168"/>
-      <c r="J25" s="168"/>
-      <c r="K25" s="168"/>
-      <c r="L25" s="168"/>
-      <c r="M25" s="168"/>
-      <c r="N25" s="168"/>
-      <c r="O25" s="168"/>
+      <c r="D25" s="164"/>
+      <c r="E25" s="164"/>
+      <c r="F25" s="164"/>
+      <c r="G25" s="164"/>
+      <c r="H25" s="164"/>
+      <c r="I25" s="164"/>
+      <c r="J25" s="164"/>
+      <c r="K25" s="164"/>
+      <c r="L25" s="164"/>
+      <c r="M25" s="164"/>
+      <c r="N25" s="164"/>
+      <c r="O25" s="164"/>
     </row>
     <row r="26" spans="1:17" ht="65.25" customHeight="1">
-      <c r="D26" s="168"/>
-      <c r="E26" s="168"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="168"/>
-      <c r="I26" s="168"/>
-      <c r="J26" s="168"/>
-      <c r="K26" s="168"/>
-      <c r="L26" s="168"/>
-      <c r="M26" s="168"/>
-      <c r="N26" s="168"/>
-      <c r="O26" s="168"/>
+      <c r="D26" s="164"/>
+      <c r="E26" s="164"/>
+      <c r="F26" s="164"/>
+      <c r="G26" s="164"/>
+      <c r="H26" s="164"/>
+      <c r="I26" s="164"/>
+      <c r="J26" s="164"/>
+      <c r="K26" s="164"/>
+      <c r="L26" s="164"/>
+      <c r="M26" s="164"/>
+      <c r="N26" s="164"/>
+      <c r="O26" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="D21:O26"/>
@@ -3769,11 +3799,6 @@
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
